--- a/outputs/Estadistica Ejercicio/Heatmap/Resumenes_Llamadas/Resumen_categoria.xlsx
+++ b/outputs/Estadistica Ejercicio/Heatmap/Resumenes_Llamadas/Resumen_categoria.xlsx
@@ -35,88 +35,88 @@
     <t xml:space="preserve">Mineral de la Reforma</t>
   </si>
   <si>
+    <t xml:space="preserve">Tlanalapa</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tula de Allende</t>
   </si>
   <si>
+    <t xml:space="preserve">Tepeji del Río de Ocampo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapotlán de Juárez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tepeapulco</t>
   </si>
   <si>
-    <t xml:space="preserve">Tlanalapa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Apan</t>
   </si>
   <si>
-    <t xml:space="preserve">Tepeji del Río de Ocampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zapotlán de Juárez</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alteración del orden público</t>
   </si>
   <si>
     <t xml:space="preserve">Tizayuca</t>
   </si>
   <si>
+    <t xml:space="preserve">Tlahuelilpan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zempoala</t>
   </si>
   <si>
-    <t xml:space="preserve">Tlahuelilpan</t>
+    <t xml:space="preserve">Amenazas, extorsión y conductas sospechosas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singuilucan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epazoyucan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago Tulantepec de Lugo Guerrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armas, explosivos y pirotecnia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omitlán de Juárez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daños a bienes y propiedad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetepango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delitos en materia de hidrocarburos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chapantongo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nopala de Villagrán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajacuba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuautepec de Hinojosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tlaxcoapan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delitos sexuales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mineral del Monte</t>
   </si>
   <si>
     <t xml:space="preserve">Atotonilco de Tula</t>
   </si>
   <si>
     <t xml:space="preserve">Actopan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amenazas, extorsión y conductas sospechosas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Singuilucan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epazoyucan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago Tulantepec de Lugo Guerrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armas, explosivos y pirotecnia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Omitlán de Juárez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daños a bienes y propiedad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tetepango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delitos en materia de hidrocarburos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chapantongo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nopala de Villagrán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajacuba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuautepec de Hinojosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tlaxcoapan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delitos sexuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineral del Monte</t>
   </si>
   <si>
     <t xml:space="preserve">Fraude y abuso patrimonial</t>
@@ -485,7 +485,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3299</v>
+        <v>3.2482</v>
       </c>
     </row>
     <row r="3">
@@ -496,7 +496,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>6.266</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="4">
@@ -507,7 +507,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>5.5882</v>
+        <v>1.8496</v>
       </c>
     </row>
     <row r="5">
@@ -518,7 +518,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.0397</v>
+        <v>1.3498</v>
       </c>
     </row>
     <row r="6">
@@ -529,7 +529,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.627</v>
+        <v>1.2944</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4194</v>
+        <v>1.2259</v>
       </c>
     </row>
     <row r="8">
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2776</v>
+        <v>1.1659</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3.1917</v>
+        <v>1.1379</v>
       </c>
     </row>
     <row r="10">
@@ -573,7 +573,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>3.0313</v>
+        <v>1.0497</v>
       </c>
     </row>
     <row r="11">
@@ -584,7 +584,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8358</v>
+        <v>23.9175</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>11.4624</v>
+        <v>15.2011</v>
       </c>
     </row>
     <row r="13">
@@ -606,7 +606,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>9.5445</v>
+        <v>13.8505</v>
       </c>
     </row>
     <row r="14">
@@ -617,62 +617,62 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.2352</v>
+        <v>9.7622</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>6.6894</v>
+        <v>9.4347</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>6.2688</v>
+        <v>8.1252</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>5.9789</v>
+        <v>7.7621</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>5.8108</v>
+        <v>7.6867</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>5.7539</v>
+        <v>7.5985</v>
       </c>
     </row>
     <row r="20">
@@ -680,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
         <v>13.1008</v>
@@ -691,7 +691,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
         <v>9.7227</v>
@@ -702,7 +702,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" t="n">
         <v>8.4834</v>
@@ -710,10 +710,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" t="n">
         <v>6.8197</v>
@@ -721,10 +721,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C24" t="n">
         <v>5.6796</v>
@@ -732,10 +732,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C25" t="n">
         <v>5.4744</v>
@@ -743,10 +743,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C26" t="n">
         <v>5.4227</v>
@@ -754,10 +754,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C27" t="n">
         <v>4.8511</v>
@@ -765,10 +765,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C28" t="n">
         <v>4.7774</v>
@@ -779,7 +779,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C29" t="n">
         <v>3.0825</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C30" t="n">
         <v>2.4296</v>
@@ -801,7 +801,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C31" t="n">
         <v>2.3733</v>
@@ -809,10 +809,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C32" t="n">
         <v>2.3141</v>
@@ -820,10 +820,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C33" t="n">
         <v>2.0763</v>
@@ -831,10 +831,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C34" t="n">
         <v>1.8846</v>
@@ -842,10 +842,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C35" t="n">
         <v>1.8289</v>
@@ -856,7 +856,7 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C36" t="n">
         <v>1.8151</v>
@@ -867,7 +867,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C37" t="n">
         <v>1.7528</v>
@@ -878,7 +878,7 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C38" t="n">
         <v>3.9831</v>
@@ -889,7 +889,7 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C39" t="n">
         <v>3.3786</v>
@@ -900,7 +900,7 @@
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C40" t="n">
         <v>2.6608</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C41" t="n">
         <v>2.337</v>
@@ -922,7 +922,7 @@
         <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C42" t="n">
         <v>2.1984</v>
@@ -930,10 +930,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C43" t="n">
         <v>1.965</v>
@@ -941,10 +941,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C44" t="n">
         <v>1.9024</v>
@@ -952,10 +952,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C45" t="n">
         <v>1.8133</v>
@@ -963,10 +963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C46" t="n">
         <v>1.7694</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C47" t="n">
         <v>2.7192</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C48" t="n">
         <v>2.2364</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C49" t="n">
         <v>1.1801</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C50" t="n">
         <v>1.1657</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C51" t="n">
         <v>1.0427</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C52" t="n">
         <v>0.6987</v>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C53" t="n">
         <v>0.5944</v>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C54" t="n">
         <v>0.5908</v>
@@ -1062,10 +1062,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C55" t="n">
         <v>0.5814</v>
@@ -1076,7 +1076,7 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C56" t="n">
         <v>0.9385</v>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C57" t="n">
         <v>0.6313</v>
@@ -1098,7 +1098,7 @@
         <v>5</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C58" t="n">
         <v>0.4455</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C59" t="n">
         <v>0.3491</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C60" t="n">
         <v>0.3475</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C61" t="n">
         <v>0.3281</v>
@@ -1142,7 +1142,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C62" t="n">
         <v>0.2733</v>
@@ -1150,10 +1150,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C63" t="n">
         <v>0.2401</v>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C64" t="n">
         <v>0.2295</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B68" t="s">
         <v>35</v>
@@ -1249,7 +1249,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
         <v>35</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
         <v>35</v>
@@ -1304,7 +1304,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B77" t="s">
         <v>38</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
         <v>38</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B79" t="s">
         <v>38</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
         <v>38</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B81" t="s">
         <v>38</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B87" t="s">
         <v>39</v>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
         <v>39</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B89" t="s">
         <v>39</v>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B91" t="s">
         <v>39</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
         <v>41</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
         <v>41</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B98" t="s">
         <v>41</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B99" t="s">
         <v>41</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B100" t="s">
         <v>41</v>
